--- a/docentes/Flores González Ángel - Estadisticos 20212.xlsx
+++ b/docentes/Flores González Ángel - Estadisticos 20212.xlsx
@@ -480,16 +480,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -503,16 +506,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -526,16 +532,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>94.29000000000001</v>
+      </c>
+      <c r="H4">
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -549,16 +558,19 @@
         <v>33</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>33</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -572,16 +584,19 @@
         <v>31</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>31</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -637,7 +652,7 @@
         <v>44</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -660,7 +675,7 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -683,7 +698,7 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -706,7 +721,7 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -729,7 +744,7 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -788,16 +803,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -811,16 +829,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -834,16 +855,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>94.29000000000001</v>
+      </c>
+      <c r="H4">
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -857,16 +881,19 @@
         <v>33</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>33</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -880,16 +907,19 @@
         <v>31</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>31</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Flores González Ángel - Estadisticos 20212.xlsx
+++ b/docentes/Flores González Ángel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -80,6 +80,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>JESE YAEL</t>
   </si>
 </sst>
 </file>
@@ -929,7 +938,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -959,6 +968,29 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920161</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Flores González Ángel - Estadisticos 20212.xlsx
+++ b/docentes/Flores González Ángel - Estadisticos 20212.xlsx
@@ -538,10 +538,10 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -550,7 +550,7 @@
         <v>33</v>
       </c>
       <c r="G4">
-        <v>94.29000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H4">
         <v>9.5</v>
@@ -701,10 +701,10 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>33</v>
@@ -861,10 +861,10 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -873,7 +873,7 @@
         <v>33</v>
       </c>
       <c r="G4">
-        <v>94.29000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H4">
         <v>9.5</v>
@@ -988,7 +988,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Flores González Ángel - Estadisticos 20212.xlsx
+++ b/docentes/Flores González Ángel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,15 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>JESE YAEL</t>
   </si>
 </sst>
 </file>
@@ -541,19 +532,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -658,16 +649,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -681,16 +675,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -704,16 +701,19 @@
         <v>34</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>34</v>
       </c>
-      <c r="E4">
-        <v>33</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>9.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -727,16 +727,19 @@
         <v>33</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>33</v>
       </c>
-      <c r="E5">
-        <v>33</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -750,16 +753,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>96.77</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +830,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -850,7 +856,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -864,19 +870,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -902,7 +908,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -919,16 +925,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>96.77</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -938,7 +944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -968,29 +974,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920161</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Flores González Ángel - Estadisticos 20212.xlsx
+++ b/docentes/Flores González Ángel - Estadisticos 20212.xlsx
@@ -830,7 +830,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -856,7 +856,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -882,7 +882,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
